--- a/data/trans_bre/IP22_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP22_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 13,04</t>
+          <t>-5,76; 13,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 16,17</t>
+          <t>-2,42; 15,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 10,61</t>
+          <t>-6,05; 10,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 17,37</t>
+          <t>-6,84; 17,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-18,0; 60,61</t>
+          <t>-18,16; 57,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 69,13</t>
+          <t>-8,58; 65,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-24,79; 70,59</t>
+          <t>-26,88; 69,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-29,04; 109,08</t>
+          <t>-26,41; 109,74</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,72; -1,03</t>
+          <t>-12,97; -1,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 3,48</t>
+          <t>-11,27; 2,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 11,14</t>
+          <t>-1,01; 11,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,17; 4,27</t>
+          <t>-9,94; 4,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-41,65; -4,11</t>
+          <t>-42,79; -4,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-28,41; 10,25</t>
+          <t>-29,37; 8,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 83,93</t>
+          <t>-4,55; 85,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-44,37; 34,09</t>
+          <t>-48,29; 30,08</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 9,29</t>
+          <t>-5,15; 9,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,31; 3,49</t>
+          <t>-9,89; 3,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 6,24</t>
+          <t>-6,54; 5,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 5,25</t>
+          <t>-8,41; 5,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-27,84; 85,1</t>
+          <t>-29,24; 82,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-48,1; 27,56</t>
+          <t>-48,27; 26,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-30,72; 49,3</t>
+          <t>-34,24; 41,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-41,53; 41,46</t>
+          <t>-43,6; 39,94</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 3,08</t>
+          <t>-8,5; 3,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,04; -6,03</t>
+          <t>-19,54; -6,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 1,25</t>
+          <t>-11,81; 1,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 9,27</t>
+          <t>-4,49; 9,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-44,75; 22,58</t>
+          <t>-44,61; 25,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-70,92; -31,03</t>
+          <t>-71,25; -31,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-54,4; 12,96</t>
+          <t>-58,27; 12,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,19; 86,73</t>
+          <t>-29,17; 89,73</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 1,05</t>
+          <t>-5,75; 0,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,6; -0,11</t>
+          <t>-7,8; -0,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 4,08</t>
+          <t>-2,53; 4,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 4,05</t>
+          <t>-3,7; 4,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-26,04; 5,33</t>
+          <t>-25,19; 3,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,64; 0,04</t>
+          <t>-26,5; 0,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-12,69; 27,05</t>
+          <t>-13,6; 25,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-23,18; 29,0</t>
+          <t>-22,11; 31,36</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP22_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP22_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,68</t>
+          <t>4,92</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>23,61%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 13,2</t>
+          <t>-5,88; 13,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 15,24</t>
+          <t>-2,21; 15,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 10,26</t>
+          <t>-5,99; 10,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 17,13</t>
+          <t>-7,6; 16,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-18,16; 57,04</t>
+          <t>-18,43; 63,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 65,92</t>
+          <t>-6,63; 68,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-26,88; 69,78</t>
+          <t>-24,73; 71,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-26,41; 109,74</t>
+          <t>-27,01; 113,19</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,87</t>
+          <t>-2,57</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-16,72%</t>
+          <t>-15,74%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,97; -1,06</t>
+          <t>-12,85; -1,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 2,83</t>
+          <t>-10,81; 2,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 11,2</t>
+          <t>-0,46; 11,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,94; 4,04</t>
+          <t>-9,02; 4,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-42,79; -4,42</t>
+          <t>-42,47; -4,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-29,37; 8,69</t>
+          <t>-28,06; 8,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 85,16</t>
+          <t>-3,68; 80,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-48,29; 30,08</t>
+          <t>-47,15; 34,42</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,34</t>
+          <t>-1,29</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-8,28%</t>
+          <t>-8,03%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 9,66</t>
+          <t>-4,88; 9,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 3,55</t>
+          <t>-9,15; 4,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 5,51</t>
+          <t>-6,74; 5,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 5,2</t>
+          <t>-7,92; 5,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-29,24; 82,46</t>
+          <t>-26,93; 90,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-48,27; 26,54</t>
+          <t>-45,58; 28,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-34,24; 41,35</t>
+          <t>-35,28; 44,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-43,6; 39,94</t>
+          <t>-41,54; 42,07</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,05</t>
+          <t>1,56</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>12,32%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 3,21</t>
+          <t>-8,27; 2,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,54; -6,68</t>
+          <t>-19,82; -6,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,81; 1,37</t>
+          <t>-10,87; 1,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 9,25</t>
+          <t>-4,14; 7,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-44,61; 25,46</t>
+          <t>-44,25; 22,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-71,25; -31,48</t>
+          <t>-71,48; -32,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-58,27; 12,5</t>
+          <t>-54,85; 10,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-29,17; 89,73</t>
+          <t>-26,87; 74,17</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,18</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 0,69</t>
+          <t>-5,68; 1,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,8; -0,05</t>
+          <t>-7,63; -0,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 4,04</t>
+          <t>-2,54; 3,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 4,26</t>
+          <t>-3,39; 3,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-25,19; 3,69</t>
+          <t>-23,91; 5,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-26,5; 0,0</t>
+          <t>-26,0; -2,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 25,62</t>
+          <t>-13,56; 25,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-22,11; 31,36</t>
+          <t>-19,9; 23,22</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP22_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP22_R-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -522,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han utilizado las urgencias en el último año</t>
+          <t>Menores que han utilizado  algún servicio de urgencias en los últimos 12 meses</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>3,72</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,43</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,92</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>13,52%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>25,21%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,56%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>23,61%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>3.718461266424216</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>6.998941557569665</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2.429921320362691</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>4.923742749543583</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.1352274861182927</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.2520793600116435</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.1256298507506494</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.2361358306281015</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-5,88; 13,64</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-2,21; 15,46</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-5,99; 10,37</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-7,6; 16,51</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-18,43; 63,92</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-6,63; 68,81</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-24,73; 71,84</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-27,01; 113,19</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-5.875943896417176</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-2.209285458629203</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-5.986307665386691</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-7.596273632673061</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.1842961124749148</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.06627085258459675</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.2472886048488682</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.2701362667717731</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>13.63928773511553</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>15.45650814693408</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>10.3747357501537</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>16.50667971125407</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.6391608426579214</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.6880955014166721</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.7183686853665536</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>1.131895541032782</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-6,92</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-3,94</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5,15</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-2,57</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-25,48%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-10,98%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>31,47%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-15,74%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-12,85; -1,0</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-10,81; 2,89</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-0,46; 11,22</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-9,02; 4,29</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-42,47; -4,05</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-28,06; 8,98</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-3,68; 80,32</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-47,15; 34,42</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-6.923705336255318</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-3.94283113673205</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>5.146647166796431</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-2.567193474455426</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.2548382027697161</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.1098259629412659</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.3146614230454737</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.1573876719755049</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1,84</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-2,98</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,22</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,29</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>12,54%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-17,16%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-1,33%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-8,03%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-12.85147046184989</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-10.81327094935118</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-0.4595383290670432</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-9.019082305509549</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.4247118202939291</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.2806239080296074</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.03677264108457407</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.4715478234243042</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-4,88; 9,78</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-9,15; 4,02</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-6,74; 5,78</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-7,92; 5,33</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-26,93; 90,21</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-45,58; 28,79</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-35,28; 44,07</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-41,54; 42,07</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>-1.000322834251041</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.889176170850651</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>11.21580198829733</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>4.287830062451555</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>-0.04045022661941702</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.0898161695670228</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.8031613254757365</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.3442259920600009</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-2,98</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-12,9</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-4,5</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,56</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-18,12%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-53,94%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-28,52%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12,32%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>1.844038909898899</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-2.98437478757412</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.2185331170214355</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-1.293128081317596</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.1254012130732163</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.1715741874128826</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.01330916960476796</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.08030686656517673</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-8,27; 2,57</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-19,82; -6,44</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-10,87; 1,22</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-4,14; 7,5</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-44,25; 22,72</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-71,48; -32,17</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-54,85; 10,36</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-26,87; 74,17</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-4.882359953922892</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-9.151354124652045</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-6.743062787644099</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-7.915643509930384</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.2692816811727388</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.4557689110313167</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.3528018188171365</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.4153853200969376</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>9.780395911847272</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>4.017835322950852</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>5.784528686144444</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>5.333332845782221</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.9020806567008922</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.287852286397254</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.4407093194520637</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.4207414500090408</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-2.980435398602099</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-12.89847065313541</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-4.501498068955486</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>1.564946127718597</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.181158851039418</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.5393622847004746</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.2852255401258762</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.1232256099796891</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-8.265754044859287</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-19.82387308997009</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-10.87437450172992</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-4.140200371985122</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.4425369233234582</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.7147546039814191</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.5484892680179625</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.2687365877149619</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2.570397921058859</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>-6.443000326251222</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.22037494228825</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>7.498183760798592</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.2272471097146564</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>-0.3216943475827726</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.103617724709637</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.7417171653240577</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-2,4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-3,95</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,88</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,18</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-11,02%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-14,34%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,25%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-5,68; 1,12</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-7,63; -0,57</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-2,54; 3,98</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-3,39; 3,12</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-23,91; 5,77</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-26,0; -2,41</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-13,56; 25,72</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-19,9; 23,22</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-2.395243699631203</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-3.951215835661404</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.8793921301998214</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.1784846026985448</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.11023703047662</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.1433537543539037</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.05254208755299705</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.0118429359520068</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-5.683167801245338</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-7.633143900470583</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-2.536614228061019</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-3.394341413295825</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.239099318417747</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.2599869066372418</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.1356287668745965</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.1989651775937161</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.124251567039551</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>-0.5685704669599559</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.97682930800347</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>3.122609584085534</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.05770113239555569</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>-0.02406515862058242</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.2572264989565686</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.2321734457508141</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
